--- a/marketing-tracker/seasonal_moments_template.xlsx
+++ b/marketing-tracker/seasonal_moments_template.xlsx
@@ -12119,7 +12119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12336,10 +12336,34 @@
     <row r="9">
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cross-vertical</t>
+          <t>Royal Club</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>RCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Snoonu Plus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cross-vertical</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>CVT</t>
         </is>
